--- a/public/templates-xlsx/analisis_suelo.xlsx
+++ b/public/templates-xlsx/analisis_suelo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -47,6 +47,12 @@
   </si>
   <si>
     <t xml:space="preserve">Lote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caracterizacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Textura</t>
   </si>
   <si>
     <t xml:space="preserve">Profundidad (cm)</t>
@@ -208,7 +214,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.3"/>
@@ -346,6 +352,16 @@
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
